--- a/ig/DM-37/ValueSet-JDV-J186-ProfessionRessource-ROR.xlsx
+++ b/ig/DM-37/ValueSet-JDV-J186-ProfessionRessource-ROR.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="302">
   <si>
     <t>Property</t>
   </si>
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-26T12:00:00+01:00</t>
+    <t>2024-04-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -916,6 +916,12 @@
   </si>
   <si>
     <t>Réanimateur néonatologiste</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>Conseiller conjugal et familial</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R356-ProfessionRessource/FHIR/TRE-R356-ProfessionRessource</t>
@@ -1856,7 +1862,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B98"/>
+  <dimension ref="A1:B99"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2633,18 +2639,26 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>88</v>
+        <v>299</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>88</v>
+        <v>300</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="B98" t="s" s="2">
-        <v>299</v>
+      <c r="B99" t="s" s="2">
+        <v>301</v>
       </c>
     </row>
   </sheetData>
